--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104566_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104566_W12.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6154</v>
+        <v>3.8296</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6116</v>
+        <v>4.8307</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9963</v>
+        <v>-1.001</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1958</v>
+        <v>1.207</v>
       </c>
       <c r="H2" t="n">
-        <v>0.58</v>
+        <v>0.5856</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6158</v>
+        <v>0.6214</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3487</v>
+        <v>2.3395</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7144</v>
+        <v>1.7064</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.153</v>
+        <v>-1.1325</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5804</v>
+        <v>-0.3774</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4688</v>
+        <v>-0.2325</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1116</v>
+        <v>-0.1449</v>
       </c>
       <c r="V2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. TAVARES</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6069</v>
+        <v>2.896</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7273</v>
+        <v>2.5464</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8795</v>
+        <v>0.3495</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6124</v>
+        <v>0.8005</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6954</v>
+        <v>0.4025</v>
       </c>
       <c r="I3" t="n">
-        <v>0.917</v>
+        <v>0.398</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1926</v>
+        <v>1.2158</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0434</v>
+        <v>1.1786</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1493</v>
+        <v>0.0372</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4197</v>
+        <v>-0.4154</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.348</v>
+        <v>-0.7761</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7678</v>
+        <v>0.3608</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4067</v>
+        <v>0.0256</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5989</v>
+        <v>0.0834</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8078</v>
+        <v>-0.0578</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0927</v>
+        <v>0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6105</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4822</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3045</v>
+        <v>2.2863</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5767</v>
+        <v>-1.2273</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8813</v>
+        <v>3.5136</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.929</v>
+        <v>-1.9363</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.1155</v>
+        <v>-2.1085</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1865</v>
+        <v>0.1722</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.7729</v>
+        <v>-2.8136</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5625</v>
+        <v>-1.576</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2104</v>
+        <v>-1.2376</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8439</v>
+        <v>0.8773</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.553</v>
+        <v>-0.5325</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3968</v>
+        <v>1.4097</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.999</v>
+        <v>0.0013</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5474</v>
+        <v>-0.04</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4515</v>
+        <v>0.0413</v>
       </c>
       <c r="V4" t="n">
-        <v>5.1419</v>
+        <v>5.1318</v>
       </c>
       <c r="W4" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>E. TAVARES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1921</v>
+        <v>2.1455</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8062</v>
+        <v>0.8858</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3859</v>
+        <v>1.2598</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8018</v>
+        <v>2.6297</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4099</v>
+        <v>1.7027</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3919</v>
+        <v>0.927</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2353</v>
+        <v>2.1829</v>
       </c>
       <c r="K5" t="n">
-        <v>1.198</v>
+        <v>2.0339</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0373</v>
+        <v>0.1489</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4335</v>
+        <v>0.4468</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.788</v>
+        <v>-0.3312</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3546</v>
+        <v>0.778</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3242</v>
+        <v>-0.0776</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3176</v>
+        <v>-0.2257</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0066</v>
+        <v>0.1481</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9320000000000001</v>
+        <v>-1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2534</v>
+        <v>-0.6162</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3214</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9349</v>
+        <v>1.861</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5517</v>
+        <v>0.5429</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3831</v>
+        <v>1.3181</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3533</v>
+        <v>1.372</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5482</v>
+        <v>0.5567</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8051</v>
+        <v>0.8153</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5785</v>
+        <v>1.5713</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5412</v>
+        <v>1.5341</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2252</v>
+        <v>-0.1993</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.993</v>
+        <v>-0.9774</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0989</v>
+        <v>-0.1939</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1875</v>
+        <v>-0.1862</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0886</v>
+        <v>-0.0077</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8923</v>
+        <v>1.6574</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0886</v>
+        <v>2.5106</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1962</v>
+        <v>-0.8531</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.7397</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.515</v>
+        <v>-0.525</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2635</v>
+        <v>1.2647</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9333</v>
+        <v>1.901</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9657</v>
+        <v>0.9405</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1848</v>
+        <v>-1.1613</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4807</v>
+        <v>-1.4656</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9073</v>
+        <v>-0.1231</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4688</v>
+        <v>0.0044</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4386</v>
+        <v>-0.1275</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W7" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7127</v>
+        <v>0.9036999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1219</v>
+        <v>2.1109</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4092</v>
+        <v>-1.2072</v>
       </c>
       <c r="G8" t="n">
-        <v>2.657</v>
+        <v>2.6597</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1399</v>
+        <v>2.1397</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5171</v>
+        <v>0.52</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5392</v>
+        <v>2.5291</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9048</v>
+        <v>1.8961</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1178</v>
+        <v>0.1306</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0785</v>
+        <v>-0.8942</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4174</v>
+        <v>-0.4182</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6611</v>
+        <v>-0.476</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2357</v>
+        <v>0.7598</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0973</v>
+        <v>1.4377</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8616</v>
+        <v>-0.678</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.733</v>
+        <v>-1.7174</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4532</v>
+        <v>-1.4451</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2798</v>
+        <v>-0.2723</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3126</v>
+        <v>0.3046</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2007</v>
+        <v>0.1929</v>
       </c>
       <c r="L9" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0457</v>
+        <v>-2.0219</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6539</v>
+        <v>-1.638</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.1359</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4688</v>
+        <v>-0.1141</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1769</v>
+        <v>-0.0218</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,22 +1189,22 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7195</v>
+        <v>-0.7171</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7195</v>
+        <v>-0.7171</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7195</v>
+        <v>-0.7171</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1216,13 +1216,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7195</v>
+        <v>-0.7171</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3234</v>
+        <v>-1.5085</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.27</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0534</v>
+        <v>-0.5483</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4565</v>
+        <v>3.4519</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8096</v>
+        <v>0.8017</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6469</v>
+        <v>2.6502</v>
       </c>
       <c r="J11" t="n">
-        <v>2.565</v>
+        <v>2.5313</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0004</v>
+        <v>0.975</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5646</v>
+        <v>1.5563</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8915</v>
+        <v>0.9206</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O11" t="n">
-        <v>1.0823</v>
+        <v>1.0939</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0067</v>
+        <v>-1.188</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.113</v>
+        <v>-0.7599</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8937</v>
+        <v>-0.4281</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6123</v>
+        <v>-4.2715</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1957</v>
+        <v>-4.0031</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4166</v>
+        <v>-0.2684</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.8845</v>
+        <v>-4.8963</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2598</v>
+        <v>-0.2586</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.6248</v>
+        <v>-4.6377</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.707</v>
+        <v>-4.7403</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1008</v>
+        <v>-0.1142</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.6062</v>
+        <v>-4.6261</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1776</v>
+        <v>-0.156</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.159</v>
+        <v>-0.1444</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4348</v>
+        <v>-1.0777</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8347</v>
+        <v>-0.5995</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6001</v>
+        <v>-0.4782</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.839300000000001</v>
+        <v>9.842200000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>8.962200000000001</v>
+        <v>8.6744</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8769999999999996</v>
+        <v>1.1679</v>
       </c>
       <c r="G13" t="n">
-        <v>3.559299999999999</v>
+        <v>3.593400000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4932</v>
+        <v>1.507</v>
       </c>
       <c r="I13" t="n">
-        <v>2.066</v>
+        <v>2.0864</v>
       </c>
       <c r="J13" t="n">
-        <v>7.2253</v>
+        <v>7.021599999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>8.9053</v>
+        <v>8.767299999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.6798</v>
+        <v>-1.7459</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.6664</v>
+        <v>-3.4282</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.412000000000001</v>
+        <v>-7.260400000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>3.7458</v>
+        <v>3.832100000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2684</v>
+        <v>2.276399999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.073399999999999</v>
+        <v>-9.105399999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>11.3418</v>
+        <v>11.3818</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.022400000000001</v>
+        <v>-4.0409</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.4951</v>
+        <v>-2.4883</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5275</v>
+        <v>-1.5526</v>
       </c>
       <c r="V13" t="n">
-        <v>8.034300000000002</v>
+        <v>8.0131</v>
       </c>
       <c r="W13" t="n">
-        <v>13.3052</v>
+        <v>13.2462</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.270899999999999</v>
+        <v>-5.233</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. RUBIT</t>
+          <t>A. DIAZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7641</v>
+        <v>2.4469</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1606</v>
+        <v>2.6479</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6035</v>
+        <v>-0.201</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.0595</v>
+        <v>1.3613</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4487</v>
+        <v>0.5972</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3892</v>
+        <v>0.764</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.6091</v>
+        <v>1.7622</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.6837</v>
+        <v>0.7272</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0746</v>
+        <v>1.035</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5496</v>
+        <v>-0.4009</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2351</v>
+        <v>-0.13</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3145</v>
+        <v>-0.271</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3699</v>
+        <v>0.6516</v>
       </c>
       <c r="T14" t="n">
-        <v>1.609</v>
+        <v>0.1833</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7609</v>
+        <v>0.4683</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5463</v>
+        <v>-0.9317</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3856</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DIAZ</t>
+          <t>A. RUBIT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2433</v>
+        <v>1.7537</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3143</v>
+        <v>-0.6772</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0711</v>
+        <v>2.431</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3621</v>
+        <v>-1.0627</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5945</v>
+        <v>-1.453</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.3903</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7797</v>
+        <v>-1.6222</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7375</v>
+        <v>-1.6967</v>
       </c>
       <c r="L15" t="n">
-        <v>1.0422</v>
+        <v>0.0745</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4176</v>
+        <v>0.5595</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1431</v>
+        <v>0.2437</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2745</v>
+        <v>0.3159</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4521</v>
+        <v>1.3612</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1724</v>
+        <v>0.7872</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.574</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7071</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.639</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7322</v>
+        <v>1.6496</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8293</v>
+        <v>1.6853</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0357</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1749</v>
+        <v>2.1736</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6925</v>
+        <v>1.6971</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1706</v>
+        <v>3.1481</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3551</v>
+        <v>2.3442</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8156</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9957</v>
+        <v>-0.9745</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.65</v>
+        <v>0.5655</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4053</v>
+        <v>0.29</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2447</v>
+        <v>0.2755</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4539</v>
+        <v>0.6482</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6489</v>
+        <v>1.6613</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.195</v>
+        <v>-1.0131</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1024</v>
+        <v>0.1013</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3663</v>
+        <v>-1.3752</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4688</v>
+        <v>1.4766</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6604</v>
+        <v>1.635</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4289</v>
+        <v>0.4062</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5579</v>
+        <v>-1.5337</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7953</v>
+        <v>-1.7814</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2945</v>
+        <v>0.5108</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3852</v>
+        <v>0.4455</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0907</v>
+        <v>0.0653</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9643</v>
+        <v>0.9466</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9643</v>
+        <v>0.9466</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. AUDIGE</t>
+          <t>C. DUARTE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5654</v>
+        <v>-0.5536</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4148</v>
+        <v>1.2206</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1505</v>
+        <v>-1.7742</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6855</v>
+        <v>0.4757</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7331</v>
+        <v>-0.9676</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0476</v>
+        <v>1.4433</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3272</v>
+        <v>0.6762</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0016</v>
+        <v>0.6992</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6744</v>
+        <v>-0.023</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6417</v>
+        <v>-0.2006</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2685</v>
+        <v>-1.6668</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3732</v>
+        <v>1.4663</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3369</v>
+        <v>0.5642</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5263</v>
+        <v>0.3246</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1893</v>
+        <v>0.2396</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>C. AUDIGE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9709</v>
+        <v>-0.7059</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0959</v>
+        <v>-0.9132</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0668</v>
+        <v>0.2073</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0112</v>
+        <v>0.6762</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6206</v>
+        <v>1.7265</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6318</v>
+        <v>-1.0503</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4255</v>
+        <v>1.3076</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8414</v>
+        <v>1.9855</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4159</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4368</v>
+        <v>-0.6314</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2209</v>
+        <v>-0.259</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2159</v>
+        <v>-0.3724</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.16</v>
+        <v>0.2113</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3297</v>
+        <v>0.0556</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1697</v>
+        <v>0.1557</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. DUARTE</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3266</v>
+        <v>-1.0081</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8005</v>
+        <v>0.0757</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1271</v>
+        <v>-1.0838</v>
       </c>
       <c r="G20" t="n">
-        <v>0.485</v>
+        <v>-0.0244</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9624</v>
+        <v>0.6149</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4473</v>
+        <v>-0.6394</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7151999999999999</v>
+        <v>0.4057</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.8306</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0081</v>
+        <v>-0.4249</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2302</v>
+        <v>-0.4301</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6857</v>
+        <v>-0.2157</v>
       </c>
       <c r="O20" t="n">
-        <v>1.4555</v>
+        <v>-0.2144</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2238</v>
+        <v>-0.1917</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1512</v>
+        <v>-0.33</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0726</v>
+        <v>0.1383</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W20" t="n">
-        <v>2.7317</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.7317</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2699</v>
+        <v>-1.0366</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0996</v>
+        <v>-0.3081</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1703</v>
+        <v>-0.7285</v>
       </c>
       <c r="G21" t="n">
-        <v>0.486</v>
+        <v>0.4798</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0968</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3892</v>
+        <v>0.3903</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3562</v>
+        <v>1.3253</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7348</v>
+        <v>1.713</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8702</v>
+        <v>-0.8455</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.638</v>
+        <v>-1.6235</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3664</v>
+        <v>-0.1326</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0948</v>
+        <v>-0.2676</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2716</v>
+        <v>0.135</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5186</v>
+        <v>-1.8283</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1832</v>
+        <v>0.5119</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3354</v>
+        <v>-2.3401</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3124</v>
+        <v>-1.308</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9553</v>
+        <v>-0.9536</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3572</v>
+        <v>-0.3544</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5803</v>
+        <v>-0.5913</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1314</v>
+        <v>0.1239</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7321</v>
+        <v>-0.7168</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4065</v>
+        <v>0.2717</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6956</v>
+        <v>0.0136</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2891</v>
+        <v>0.2581</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>J. WEBB III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8119</v>
+        <v>-3.3311</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5882</v>
+        <v>-2.3296</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2236</v>
+        <v>-1.0015</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.3364</v>
+        <v>-2.3218</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.876</v>
+        <v>-1.215</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.4603</v>
+        <v>-1.1068</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1357</v>
+        <v>-2.1366</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9351</v>
+        <v>-1.4586</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.0708</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2007</v>
+        <v>-0.1852</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8112</v>
+        <v>0.2437</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6105</v>
+        <v>-0.4289</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1635</v>
+        <v>0.6445</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5474</v>
+        <v>0.0346</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6161</v>
+        <v>0.6099</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-2.3367</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. WEBB III</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6207</v>
+        <v>-3.37</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4374</v>
+        <v>-1.9564</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1833</v>
+        <v>-1.4136</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.3226</v>
+        <v>-3.3291</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2164</v>
+        <v>-0.8651</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1062</v>
+        <v>-2.464</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.1259</v>
+        <v>-2.1533</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4515</v>
+        <v>0.9308</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6744</v>
+        <v>-3.0841</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1967</v>
+        <v>-1.1758</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2351</v>
+        <v>-1.7959</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4318</v>
+        <v>0.6201</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3675</v>
+        <v>0.5933</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0847</v>
+        <v>0.1969</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4521</v>
+        <v>0.3964</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.3461</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.3461</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9487</v>
+        <v>-3.7175</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0033</v>
+        <v>-2.7861</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9454</v>
+        <v>-0.9314</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.8151</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5945</v>
+        <v>0.5972</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4074</v>
+        <v>-1.4124</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3176</v>
+        <v>-0.3285</v>
       </c>
       <c r="K25" t="n">
-        <v>0.658</v>
+        <v>0.655</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.9756</v>
+        <v>-0.9835</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4954</v>
+        <v>-0.4866</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4552</v>
+        <v>-0.2195</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4174</v>
+        <v>-0.1813</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0378</v>
+        <v>-0.0381</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.8392</v>
+        <v>-9.0527</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.8770000000000007</v>
+        <v>-1.1679</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.9621</v>
+        <v>-7.8846</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.5592</v>
+        <v>-3.5932</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.493100000000001</v>
+        <v>-1.5072</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.066000000000001</v>
+        <v>-2.0864</v>
       </c>
       <c r="J26" t="n">
-        <v>3.6662</v>
+        <v>3.4282</v>
       </c>
       <c r="K26" t="n">
-        <v>7.411900000000001</v>
+        <v>7.260300000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.7456</v>
+        <v>-3.832</v>
       </c>
       <c r="M26" t="n">
-        <v>-7.2254</v>
+        <v>-7.0216</v>
       </c>
       <c r="N26" t="n">
-        <v>-8.905399999999998</v>
+        <v>-8.767300000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>1.6799</v>
+        <v>1.7457</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.2681</v>
+        <v>-2.2761</v>
       </c>
       <c r="Q26" t="n">
-        <v>-11.3416</v>
+        <v>-11.3815</v>
       </c>
       <c r="R26" t="n">
-        <v>9.073399999999999</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>4.022500000000001</v>
+        <v>4.8303</v>
       </c>
       <c r="T26" t="n">
-        <v>1.5274</v>
+        <v>1.5524</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4951</v>
+        <v>3.278</v>
       </c>
       <c r="V26" t="n">
-        <v>-8.034599999999999</v>
+        <v>-8.013300000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>5.2709</v>
+        <v>5.2331</v>
       </c>
       <c r="X26" t="n">
-        <v>-13.3054</v>
+        <v>-13.2463</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104566_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104566_W12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-5.233</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104566_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-13.2463</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
